--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="527">
   <si>
     <t>Filename</t>
   </si>
@@ -826,16 +826,25 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9619,0.0038,0.0093,0.0032</t>
-  </si>
-  <si>
-    <t>0.0032,0.0084,0.0006,0.9989</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9619,0.0038,0.0092,0.0032</t>
+  </si>
+  <si>
+    <t>0.0032,0.0084,0.0006,0.9990</t>
   </si>
   <si>
     <t>0.9771,0.0027,0.0007,0.0073</t>
   </si>
   <si>
-    <t>0.0967,0.0028,0.0043,0.9556</t>
+    <t>0.0961,0.0028,0.0042,0.9560</t>
   </si>
   <si>
     <t>0.9920,0.0031,0.0019,0.0006</t>
@@ -859,22 +868,22 @@
     <t>0.9936,0.0016,0.0012,0.0001</t>
   </si>
   <si>
-    <t>0.9928,0.0031,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.8410,0.0099,0.1233,0.0025</t>
+    <t>0.9927,0.0031,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.8408,0.0099,0.1234,0.0025</t>
   </si>
   <si>
     <t>0.0183,0.0171,0.9721,0.0011</t>
   </si>
   <si>
-    <t>0.2783,0.0006,0.8409,0.0001</t>
-  </si>
-  <si>
-    <t>0.0434,0.0135,0.9506,0.0013</t>
-  </si>
-  <si>
-    <t>0.7794,0.0010,0.2464,0.0003</t>
+    <t>0.2782,0.0006,0.8408,0.0001</t>
+  </si>
+  <si>
+    <t>0.0434,0.0135,0.9505,0.0013</t>
+  </si>
+  <si>
+    <t>0.7796,0.0010,0.2461,0.0003</t>
   </si>
   <si>
     <t>0.0016,0.9982,0.0169,0.0007</t>
@@ -892,10 +901,10 @@
     <t>0.0008,0.9995,0.0149,0.0000</t>
   </si>
   <si>
-    <t>0.4373,0.0029,0.6403,0.0027</t>
-  </si>
-  <si>
-    <t>0.1445,0.0135,0.8645,0.0026</t>
+    <t>0.4376,0.0029,0.6398,0.0027</t>
+  </si>
+  <si>
+    <t>0.1447,0.0135,0.8642,0.0026</t>
   </si>
   <si>
     <t>0.0205,0.0005,0.9897,0.0001</t>
@@ -907,58 +916,58 @@
     <t>0.0333,0.0019,0.9797,0.0004</t>
   </si>
   <si>
-    <t>0.0658,0.0012,0.9601,0.0004</t>
-  </si>
-  <si>
-    <t>0.0123,0.0013,0.9910,0.0003</t>
-  </si>
-  <si>
-    <t>0.6725,0.1918,0.0596,0.0018</t>
-  </si>
-  <si>
-    <t>0.7880,0.3293,0.0114,0.0024</t>
+    <t>0.0660,0.0012,0.9600,0.0004</t>
+  </si>
+  <si>
+    <t>0.0123,0.0013,0.9909,0.0003</t>
+  </si>
+  <si>
+    <t>0.6718,0.1924,0.0596,0.0018</t>
+  </si>
+  <si>
+    <t>0.7878,0.3295,0.0114,0.0024</t>
   </si>
   <si>
     <t>0.0035,0.0007,0.9972,0.0005</t>
   </si>
   <si>
-    <t>0.0110,0.3961,0.8299,0.0018</t>
-  </si>
-  <si>
-    <t>0.9130,0.0066,0.0505,0.0012</t>
-  </si>
-  <si>
-    <t>0.7634,0.0198,0.1522,0.0018</t>
-  </si>
-  <si>
-    <t>0.3137,0.7947,0.0253,0.0009</t>
-  </si>
-  <si>
-    <t>0.0056,0.9772,0.5068,0.0017</t>
-  </si>
-  <si>
-    <t>0.0009,0.7141,0.9563,0.0004</t>
+    <t>0.0110,0.3973,0.8294,0.0018</t>
+  </si>
+  <si>
+    <t>0.9130,0.0066,0.0504,0.0012</t>
+  </si>
+  <si>
+    <t>0.7637,0.0198,0.1518,0.0018</t>
+  </si>
+  <si>
+    <t>0.3134,0.7950,0.0253,0.0009</t>
+  </si>
+  <si>
+    <t>0.0056,0.9772,0.5072,0.0017</t>
+  </si>
+  <si>
+    <t>0.0009,0.7149,0.9561,0.0004</t>
   </si>
   <si>
     <t>0.0014,0.0035,0.9973,0.0014</t>
   </si>
   <si>
-    <t>0.0077,0.0986,0.9685,0.0013</t>
-  </si>
-  <si>
-    <t>0.1620,0.0022,0.8477,0.0043</t>
-  </si>
-  <si>
-    <t>0.0006,0.7278,0.9450,0.0011</t>
+    <t>0.0076,0.0989,0.9685,0.0013</t>
+  </si>
+  <si>
+    <t>0.1620,0.0022,0.8475,0.0043</t>
+  </si>
+  <si>
+    <t>0.0006,0.7282,0.9449,0.0011</t>
   </si>
   <si>
     <t>0.0011,0.9911,0.0123,0.0033</t>
   </si>
   <si>
-    <t>0.0021,0.0478,0.9905,0.0019</t>
-  </si>
-  <si>
-    <t>0.0003,0.8313,0.0012,0.9624</t>
+    <t>0.0021,0.0479,0.9905,0.0019</t>
+  </si>
+  <si>
+    <t>0.0003,0.8309,0.0012,0.9625</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
@@ -973,31 +982,31 @@
     <t>0.0003,0.0122,0.9970,0.0014</t>
   </si>
   <si>
-    <t>0.0007,0.1793,0.9908,0.0015</t>
+    <t>0.0007,0.1795,0.9908,0.0015</t>
   </si>
   <si>
     <t>0.0067,0.0054,0.9900,0.0009</t>
   </si>
   <si>
-    <t>0.0236,0.0003,0.9906,0.0001</t>
+    <t>0.0237,0.0003,0.9906,0.0001</t>
   </si>
   <si>
     <t>0.0083,0.0017,0.9929,0.0001</t>
   </si>
   <si>
-    <t>0.0263,0.0190,0.9604,0.0013</t>
-  </si>
-  <si>
-    <t>0.9750,0.0100,0.0077,0.0003</t>
-  </si>
-  <si>
-    <t>0.9705,0.0008,0.0232,0.0002</t>
-  </si>
-  <si>
-    <t>0.9633,0.0215,0.0125,0.0061</t>
-  </si>
-  <si>
-    <t>0.3107,0.0022,0.7372,0.0005</t>
+    <t>0.0264,0.0191,0.9603,0.0013</t>
+  </si>
+  <si>
+    <t>0.9750,0.0100,0.0076,0.0003</t>
+  </si>
+  <si>
+    <t>0.9705,0.0008,0.0231,0.0002</t>
+  </si>
+  <si>
+    <t>0.9632,0.0215,0.0125,0.0061</t>
+  </si>
+  <si>
+    <t>0.3104,0.0022,0.7373,0.0006</t>
   </si>
   <si>
     <t>0.9845,0.0005,0.0090,0.0002</t>
@@ -1009,16 +1018,16 @@
     <t>0.9926,0.0011,0.0025,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9990,0.9263,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.2049,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0211,0.9933,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.9836,0.9115,0.0004</t>
+    <t>0.0000,0.9990,0.9262,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.2052,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0212,0.9933,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.9836,0.9114,0.0004</t>
   </si>
   <si>
     <t>0.0003,0.0006,0.9995,0.0003</t>
@@ -1030,22 +1039,22 @@
     <t>0.9802,0.0003,0.0177,0.0001</t>
   </si>
   <si>
-    <t>0.1018,0.0352,0.8722,0.0031</t>
+    <t>0.1015,0.0353,0.8723,0.0032</t>
   </si>
   <si>
     <t>0.0102,0.0037,0.9917,0.0003</t>
   </si>
   <si>
-    <t>0.0003,0.8708,0.9823,0.0005</t>
+    <t>0.0003,0.8709,0.9823,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.9341,0.9831,0.0002</t>
   </si>
   <si>
-    <t>0.0000,0.9997,0.4415,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9831,0.9735,0.0001</t>
+    <t>0.0000,0.9997,0.4412,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9831,0.9734,0.0001</t>
   </si>
   <si>
     <t>0.0012,0.0041,0.0011,0.9997</t>
@@ -1060,49 +1069,49 @@
     <t>0.0026,0.0018,0.0012,0.9996</t>
   </si>
   <si>
-    <t>0.0255,0.0021,0.0027,0.9957</t>
+    <t>0.0254,0.0021,0.0027,0.9957</t>
   </si>
   <si>
     <t>0.0005,0.0033,0.0021,0.9998</t>
   </si>
   <si>
-    <t>0.0001,0.9975,0.9098,0.0000</t>
+    <t>0.0001,0.9975,0.9096,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9324,0.9934,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.9377,0.8589,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.5532,0.9928,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9910,0.7848,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0093,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9776,0.0189,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.9711,0.0397,0.0009,0.0002</t>
+    <t>0.0003,0.9377,0.8588,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.5538,0.9928,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.9908,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9910,0.7849,0.0001</t>
+  </si>
+  <si>
+    <t>0.9906,0.0093,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9776,0.0190,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.9710,0.0398,0.0009,0.0002</t>
   </si>
   <si>
     <t>0.9910,0.0063,0.0012,0.0003</t>
   </si>
   <si>
-    <t>0.9937,0.0019,0.0012,0.0001</t>
+    <t>0.9936,0.0019,0.0012,0.0001</t>
   </si>
   <si>
     <t>0.9937,0.0023,0.0011,0.0005</t>
   </si>
   <si>
-    <t>0.9902,0.0015,0.0029,0.0004</t>
+    <t>0.9902,0.0015,0.0030,0.0004</t>
   </si>
   <si>
     <t>0.9967,0.0022,0.0008,0.0001</t>
@@ -1120,13 +1129,13 @@
     <t>0.9958,0.0017,0.0006,0.0005</t>
   </si>
   <si>
-    <t>0.9825,0.0084,0.0017,0.0016</t>
+    <t>0.9825,0.0085,0.0017,0.0016</t>
   </si>
   <si>
     <t>0.9981,0.0014,0.0003,0.0001</t>
   </si>
   <si>
-    <t>0.9941,0.0026,0.0008,0.0009</t>
+    <t>0.9940,0.0026,0.0008,0.0009</t>
   </si>
   <si>
     <t>0.9902,0.0022,0.0025,0.0003</t>
@@ -1138,7 +1147,7 @@
     <t>0.0172,0.0017,0.9873,0.0003</t>
   </si>
   <si>
-    <t>0.9652,0.0002,0.0412,0.0000</t>
+    <t>0.9652,0.0002,0.0411,0.0000</t>
   </si>
   <si>
     <t>0.0285,0.0014,0.9809,0.0002</t>
@@ -1150,10 +1159,10 @@
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.2383,0.8785,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.0354,0.9774,0.0147,0.0019</t>
+    <t>0.2381,0.8784,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.0354,0.9774,0.0146,0.0019</t>
   </si>
   <si>
     <t>0.0005,0.9996,0.0006,0.0001</t>
@@ -1162,22 +1171,22 @@
     <t>0.0001,1.0000,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.5751,0.5843,0.0192,0.0007</t>
-  </si>
-  <si>
-    <t>0.1123,0.0240,0.8750,0.0046</t>
-  </si>
-  <si>
-    <t>0.0270,0.0108,0.9691,0.0013</t>
-  </si>
-  <si>
-    <t>0.3133,0.0159,0.6639,0.0035</t>
-  </si>
-  <si>
-    <t>0.1288,0.0225,0.8728,0.0051</t>
-  </si>
-  <si>
-    <t>0.0002,0.6160,0.5035,0.2499</t>
+    <t>0.5745,0.5851,0.0192,0.0007</t>
+  </si>
+  <si>
+    <t>0.1124,0.0241,0.8747,0.0047</t>
+  </si>
+  <si>
+    <t>0.0271,0.0109,0.9691,0.0013</t>
+  </si>
+  <si>
+    <t>0.3139,0.0159,0.6631,0.0035</t>
+  </si>
+  <si>
+    <t>0.1289,0.0226,0.8726,0.0051</t>
+  </si>
+  <si>
+    <t>0.0002,0.6160,0.5032,0.2501</t>
   </si>
   <si>
     <t>0.0002,0.9999,0.0015,0.0001</t>
@@ -1195,16 +1204,16 @@
     <t>0.0030,0.9962,0.0594,0.0003</t>
   </si>
   <si>
-    <t>0.3771,0.6579,0.0617,0.0025</t>
-  </si>
-  <si>
-    <t>0.1677,0.8598,0.0250,0.0043</t>
+    <t>0.3765,0.6584,0.0617,0.0025</t>
+  </si>
+  <si>
+    <t>0.1672,0.8601,0.0250,0.0043</t>
   </si>
   <si>
     <t>0.9952,0.0006,0.0009,0.0006</t>
   </si>
   <si>
-    <t>0.9724,0.0172,0.0015,0.0025</t>
+    <t>0.9723,0.0173,0.0015,0.0025</t>
   </si>
   <si>
     <t>0.9866,0.0054,0.0019,0.0015</t>
@@ -1225,10 +1234,10 @@
     <t>0.9871,0.0014,0.0044,0.0004</t>
   </si>
   <si>
-    <t>0.0003,0.9703,0.9602,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.5027,0.9945,0.0002</t>
+    <t>0.0003,0.9703,0.9601,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.5035,0.9945,0.0002</t>
   </si>
   <si>
     <t>0.0005,0.0295,0.9980,0.0004</t>
@@ -1237,16 +1246,16 @@
     <t>0.0043,0.0084,0.9944,0.0001</t>
   </si>
   <si>
-    <t>0.9444,0.0019,0.0386,0.0004</t>
-  </si>
-  <si>
-    <t>0.3604,0.4661,0.0642,0.0050</t>
-  </si>
-  <si>
-    <t>0.1354,0.0006,0.9197,0.0007</t>
-  </si>
-  <si>
-    <t>0.8039,0.0048,0.1767,0.0019</t>
+    <t>0.9445,0.0019,0.0386,0.0004</t>
+  </si>
+  <si>
+    <t>0.3599,0.4668,0.0641,0.0050</t>
+  </si>
+  <si>
+    <t>0.1355,0.0006,0.9196,0.0007</t>
+  </si>
+  <si>
+    <t>0.8039,0.0048,0.1766,0.0019</t>
   </si>
   <si>
     <t>0.0056,0.0007,0.0020,0.9991</t>
@@ -1261,10 +1270,10 @@
     <t>0.0057,0.0005,0.0015,0.9993</t>
   </si>
   <si>
-    <t>0.0001,0.9889,0.9730,0.0001</t>
-  </si>
-  <si>
-    <t>0.9731,0.0012,0.0141,0.0006</t>
+    <t>0.0001,0.9889,0.9729,0.0001</t>
+  </si>
+  <si>
+    <t>0.9730,0.0012,0.0141,0.0006</t>
   </si>
   <si>
     <t>0.0097,0.9882,0.0178,0.0059</t>
@@ -1273,43 +1282,43 @@
     <t>0.9922,0.0008,0.0028,0.0001</t>
   </si>
   <si>
-    <t>0.0136,0.9878,0.0151,0.0010</t>
+    <t>0.0135,0.9878,0.0151,0.0010</t>
   </si>
   <si>
     <t>0.9895,0.0020,0.0015,0.0019</t>
   </si>
   <si>
-    <t>0.8056,0.0000,0.4269,0.0000</t>
-  </si>
-  <si>
-    <t>0.6976,0.0000,0.5076,0.0000</t>
+    <t>0.8056,0.0000,0.4268,0.0000</t>
+  </si>
+  <si>
+    <t>0.6971,0.0000,0.5082,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9253,0.0007,0.0436,0.0006</t>
-  </si>
-  <si>
-    <t>0.9566,0.0292,0.0093,0.0012</t>
-  </si>
-  <si>
-    <t>0.5405,0.3122,0.0397,0.0027</t>
-  </si>
-  <si>
-    <t>0.9869,0.0012,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9219,0.0284,0.0216,0.0015</t>
-  </si>
-  <si>
-    <t>0.1625,0.8052,0.0646,0.0219</t>
-  </si>
-  <si>
-    <t>0.8975,0.0265,0.0393,0.0011</t>
-  </si>
-  <si>
-    <t>0.9372,0.0022,0.0469,0.0005</t>
+    <t>0.9253,0.0007,0.0435,0.0006</t>
+  </si>
+  <si>
+    <t>0.9565,0.0292,0.0093,0.0012</t>
+  </si>
+  <si>
+    <t>0.5400,0.3126,0.0396,0.0028</t>
+  </si>
+  <si>
+    <t>0.9868,0.0012,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.9218,0.0285,0.0216,0.0015</t>
+  </si>
+  <si>
+    <t>0.1619,0.8059,0.0645,0.0220</t>
+  </si>
+  <si>
+    <t>0.8974,0.0265,0.0393,0.0011</t>
+  </si>
+  <si>
+    <t>0.9371,0.0022,0.0469,0.0005</t>
   </si>
   <si>
     <t>0.9916,0.0042,0.0016,0.0003</t>
@@ -1324,7 +1333,7 @@
     <t>0.9833,0.0020,0.0059,0.0003</t>
   </si>
   <si>
-    <t>0.9918,0.0036,0.0014,0.0002</t>
+    <t>0.9918,0.0037,0.0014,0.0002</t>
   </si>
   <si>
     <t>0.9875,0.0060,0.0022,0.0007</t>
@@ -1336,46 +1345,46 @@
     <t>0.9880,0.0022,0.0028,0.0002</t>
   </si>
   <si>
-    <t>0.6499,0.3985,0.0033,0.0019</t>
-  </si>
-  <si>
-    <t>0.1858,0.8253,0.0290,0.0124</t>
-  </si>
-  <si>
-    <t>0.8292,0.1666,0.0062,0.0011</t>
-  </si>
-  <si>
-    <t>0.9047,0.0576,0.0297,0.0032</t>
-  </si>
-  <si>
-    <t>0.9800,0.0101,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9506,0.0437,0.0063,0.0008</t>
-  </si>
-  <si>
-    <t>0.9821,0.0026,0.0080,0.0002</t>
-  </si>
-  <si>
-    <t>0.9241,0.0393,0.0191,0.0018</t>
+    <t>0.6492,0.3987,0.0033,0.0019</t>
+  </si>
+  <si>
+    <t>0.1854,0.8256,0.0289,0.0124</t>
+  </si>
+  <si>
+    <t>0.8284,0.1672,0.0062,0.0011</t>
+  </si>
+  <si>
+    <t>0.9047,0.0578,0.0297,0.0032</t>
+  </si>
+  <si>
+    <t>0.9800,0.0102,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.9505,0.0439,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.9821,0.0026,0.0080,0.0003</t>
+  </si>
+  <si>
+    <t>0.9240,0.0394,0.0190,0.0019</t>
   </si>
   <si>
     <t>0.0107,0.0035,0.9927,0.0002</t>
   </si>
   <si>
-    <t>0.9246,0.0551,0.0096,0.0004</t>
+    <t>0.9245,0.0553,0.0096,0.0004</t>
   </si>
   <si>
     <t>0.0005,0.0009,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0828,0.9918,0.0048</t>
+    <t>0.0003,0.0830,0.9918,0.0048</t>
   </si>
   <si>
     <t>0.0142,0.0026,0.9884,0.0008</t>
   </si>
   <si>
-    <t>0.0021,0.3357,0.9740,0.0008</t>
+    <t>0.0021,0.3365,0.9739,0.0008</t>
   </si>
   <si>
     <t>0.0017,0.0039,0.9975,0.0002</t>
@@ -1387,67 +1396,67 @@
     <t>0.0132,0.0018,0.9902,0.0001</t>
   </si>
   <si>
-    <t>0.0974,0.0076,0.9165,0.0012</t>
+    <t>0.0974,0.0076,0.9164,0.0012</t>
   </si>
   <si>
     <t>0.1194,0.0027,0.9154,0.0006</t>
   </si>
   <si>
-    <t>0.7421,0.0505,0.1424,0.0032</t>
-  </si>
-  <si>
-    <t>0.0602,0.0326,0.8923,0.0016</t>
-  </si>
-  <si>
-    <t>0.0130,0.0756,0.9413,0.0003</t>
+    <t>0.7422,0.0506,0.1422,0.0032</t>
+  </si>
+  <si>
+    <t>0.0602,0.0328,0.8921,0.0016</t>
+  </si>
+  <si>
+    <t>0.0130,0.0759,0.9412,0.0003</t>
   </si>
   <si>
     <t>0.0647,0.0059,0.9435,0.0012</t>
   </si>
   <si>
-    <t>0.2356,0.0083,0.7828,0.0043</t>
-  </si>
-  <si>
-    <t>0.6000,0.0608,0.2507,0.0021</t>
-  </si>
-  <si>
-    <t>0.1280,0.9503,0.0091,0.0003</t>
+    <t>0.2361,0.0083,0.7821,0.0044</t>
+  </si>
+  <si>
+    <t>0.6002,0.0610,0.2503,0.0021</t>
+  </si>
+  <si>
+    <t>0.1279,0.9503,0.0092,0.0003</t>
   </si>
   <si>
     <t>0.0021,0.9981,0.0057,0.0004</t>
   </si>
   <si>
-    <t>0.0416,0.9705,0.0047,0.0014</t>
+    <t>0.0415,0.9706,0.0047,0.0014</t>
   </si>
   <si>
     <t>0.9665,0.0163,0.0067,0.0003</t>
   </si>
   <si>
-    <t>0.3127,0.7857,0.0083,0.0007</t>
-  </si>
-  <si>
-    <t>0.2597,0.7011,0.0208,0.0005</t>
+    <t>0.3122,0.7860,0.0083,0.0007</t>
+  </si>
+  <si>
+    <t>0.2591,0.7020,0.0207,0.0005</t>
   </si>
   <si>
     <t>0.9526,0.0082,0.0144,0.0003</t>
   </si>
   <si>
-    <t>0.3632,0.0570,0.5604,0.0179</t>
-  </si>
-  <si>
-    <t>0.1064,0.0054,0.9072,0.0048</t>
-  </si>
-  <si>
-    <t>0.5774,0.0210,0.3192,0.0041</t>
+    <t>0.3632,0.0572,0.5602,0.0180</t>
+  </si>
+  <si>
+    <t>0.1063,0.0054,0.9072,0.0048</t>
+  </si>
+  <si>
+    <t>0.5778,0.0210,0.3186,0.0041</t>
   </si>
   <si>
     <t>0.0109,0.0024,0.9902,0.0006</t>
   </si>
   <si>
-    <t>0.1663,0.0061,0.8294,0.0005</t>
-  </si>
-  <si>
-    <t>0.0437,0.0629,0.8810,0.0003</t>
+    <t>0.1668,0.0061,0.8288,0.0005</t>
+  </si>
+  <si>
+    <t>0.0438,0.0631,0.8808,0.0003</t>
   </si>
   <si>
     <t>0.0026,0.0143,0.9941,0.0009</t>
@@ -1456,22 +1465,22 @@
     <t>0.0058,0.0101,0.9895,0.0002</t>
   </si>
   <si>
-    <t>0.9932,0.0008,0.0016,0.0001</t>
+    <t>0.9932,0.0008,0.0017,0.0001</t>
   </si>
   <si>
     <t>0.9762,0.0155,0.0050,0.0010</t>
   </si>
   <si>
-    <t>0.9694,0.0156,0.0037,0.0042</t>
+    <t>0.9693,0.0157,0.0037,0.0042</t>
   </si>
   <si>
     <t>0.9854,0.0109,0.0005,0.0005</t>
   </si>
   <si>
-    <t>0.9427,0.0494,0.0074,0.0031</t>
-  </si>
-  <si>
-    <t>0.9505,0.0553,0.0049,0.0020</t>
+    <t>0.9425,0.0495,0.0074,0.0031</t>
+  </si>
+  <si>
+    <t>0.9504,0.0555,0.0049,0.0020</t>
   </si>
   <si>
     <t>0.9870,0.0113,0.0016,0.0008</t>
@@ -1480,49 +1489,49 @@
     <t>0.9918,0.0015,0.0019,0.0001</t>
   </si>
   <si>
-    <t>0.0085,0.0039,0.9925,0.0007</t>
-  </si>
-  <si>
-    <t>0.0645,0.0356,0.8887,0.0011</t>
-  </si>
-  <si>
-    <t>0.4595,0.0074,0.5032,0.0179</t>
+    <t>0.0086,0.0039,0.9925,0.0007</t>
+  </si>
+  <si>
+    <t>0.0644,0.0357,0.8887,0.0011</t>
+  </si>
+  <si>
+    <t>0.4601,0.0074,0.5022,0.0180</t>
   </si>
   <si>
     <t>0.0019,0.0012,0.9984,0.0002</t>
   </si>
   <si>
-    <t>0.0003,0.0028,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0043,0.0283,0.9874,0.0007</t>
+    <t>0.0003,0.0029,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.0284,0.9873,0.0007</t>
   </si>
   <si>
     <t>0.0003,0.0001,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0124,0.0098,0.9836,0.0003</t>
+    <t>0.0124,0.0099,0.9835,0.0003</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0036,0.0089,0.9940,0.0005</t>
-  </si>
-  <si>
-    <t>0.0490,0.0149,0.9381,0.0026</t>
-  </si>
-  <si>
-    <t>0.7670,0.0025,0.2428,0.0015</t>
-  </si>
-  <si>
-    <t>0.4946,0.0018,0.4964,0.0078</t>
+    <t>0.0036,0.0090,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.0490,0.0149,0.9380,0.0027</t>
+  </si>
+  <si>
+    <t>0.7669,0.0025,0.2429,0.0016</t>
+  </si>
+  <si>
+    <t>0.4949,0.0018,0.4957,0.0078</t>
   </si>
   <si>
     <t>0.9433,0.0105,0.0209,0.0002</t>
   </si>
   <si>
-    <t>0.9930,0.0026,0.0009,0.0001</t>
+    <t>0.9929,0.0027,0.0009,0.0001</t>
   </si>
   <si>
     <t>0.9836,0.0166,0.0009,0.0006</t>
@@ -1537,16 +1546,16 @@
     <t>0.9910,0.0019,0.0020,0.0002</t>
   </si>
   <si>
-    <t>0.9812,0.0180,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0036,0.0011,0.0003</t>
+    <t>0.9812,0.0181,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0036,0.0011,0.0003</t>
   </si>
   <si>
     <t>0.9807,0.0038,0.0051,0.0025</t>
   </si>
   <si>
-    <t>0.0075,0.0291,0.9816,0.0006</t>
+    <t>0.0075,0.0292,0.9816,0.0006</t>
   </si>
   <si>
     <t>0.0011,0.0042,0.9986,0.0000</t>
@@ -1555,37 +1564,37 @@
     <t>0.0023,0.0026,0.9975,0.0001</t>
   </si>
   <si>
-    <t>0.0101,0.0648,0.9543,0.0006</t>
-  </si>
-  <si>
-    <t>0.0115,0.0023,0.9908,0.0002</t>
-  </si>
-  <si>
-    <t>0.7543,0.0656,0.0973,0.0067</t>
-  </si>
-  <si>
-    <t>0.0891,0.0335,0.8682,0.0060</t>
+    <t>0.0101,0.0651,0.9542,0.0006</t>
+  </si>
+  <si>
+    <t>0.0115,0.0023,0.9907,0.0002</t>
+  </si>
+  <si>
+    <t>0.7543,0.0657,0.0972,0.0067</t>
+  </si>
+  <si>
+    <t>0.0892,0.0336,0.8680,0.0061</t>
   </si>
   <si>
     <t>0.0016,0.0010,0.9978,0.0012</t>
   </si>
   <si>
-    <t>0.9602,0.0013,0.0047,0.0077</t>
-  </si>
-  <si>
-    <t>0.0008,0.0045,0.0002,0.9998</t>
+    <t>0.9601,0.0013,0.0047,0.0078</t>
+  </si>
+  <si>
+    <t>0.0007,0.0045,0.0002,0.9998</t>
   </si>
   <si>
     <t>0.0096,0.0003,0.0011,0.9990</t>
   </si>
   <si>
-    <t>0.0002,0.0001,0.0031,0.9999</t>
+    <t>0.0002,0.0001,0.0030,0.9999</t>
   </si>
   <si>
     <t>0.0003,0.0003,0.0011,0.9999</t>
   </si>
   <si>
-    <t>0.6420,0.0161,0.0137,0.2851</t>
+    <t>0.6410,0.0161,0.0136,0.2866</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1980,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1994,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2008,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2022,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2036,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2050,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2064,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2078,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2092,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2106,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2120,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2134,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2148,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2162,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2176,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2190,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2204,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,7 +2218,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2232,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,7 +2246,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2260,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,7 +2274,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2288,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2302,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2316,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2330,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2344,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2358,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2363,7 +2372,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2386,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2400,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2414,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2428,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2442,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2456,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2470,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,7 +2484,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,7 +2498,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2503,7 +2512,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2517,7 +2526,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2540,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,7 +2554,7 @@
         <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,7 +2568,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2573,7 +2582,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2596,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,7 +2610,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,7 +2624,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,7 +2638,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2643,7 +2652,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2657,7 +2666,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2671,7 +2680,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2694,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2708,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2722,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2736,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2750,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2764,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2778,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2792,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2806,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2820,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,7 +2834,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2839,7 +2848,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2853,7 +2862,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,7 +2876,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2881,7 +2890,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,7 +2904,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,7 +2918,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2932,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2946,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2960,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,7 +2974,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,7 +2988,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2993,7 +3002,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,7 +3016,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3030,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3044,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3058,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3072,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3086,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3100,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,7 +3114,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,7 +3128,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,7 +3142,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,7 +3156,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,7 +3170,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,7 +3184,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3198,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3212,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3226,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3240,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3254,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3268,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3282,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3296,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3310,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3324,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3338,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3352,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3366,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3380,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3394,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3408,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3413,7 +3422,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3436,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3450,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3464,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,7 +3478,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,7 +3492,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,7 +3506,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3511,7 +3520,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,7 +3534,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,7 +3548,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,10 +3559,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3576,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3590,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3604,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3618,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,7 +3632,7 @@
         <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,7 +3646,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,7 +3660,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,7 +3674,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,7 +3688,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,7 +3702,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3707,7 +3716,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3730,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3744,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3758,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3772,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3786,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3800,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3814,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3828,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3842,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,7 +3856,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,7 +3870,7 @@
         <v>268</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3875,7 +3884,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3889,7 +3898,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3912,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3923,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3940,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3954,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3968,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3982,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3996,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4010,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,7 +4024,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4038,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,7 +4052,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4066,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4080,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4094,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4108,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4119,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4136,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4150,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4164,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4178,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4192,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4206,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4220,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4234,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4248,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4262,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4276,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4290,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4304,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4318,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4332,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4346,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4360,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4374,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4388,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4402,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4416,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4430,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4444,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4458,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4472,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4486,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4500,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4505,7 +4514,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4519,7 +4528,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4542,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,7 +4556,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4561,7 +4570,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4575,7 +4584,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4598,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4612,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4626,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4640,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4654,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4668,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4682,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4696,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4710,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4724,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4738,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4752,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4766,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4780,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4794,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4808,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4822,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4836,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4850,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4864,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4878,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4892,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4897,7 +4906,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4911,7 +4920,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4934,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4948,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4962,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4976,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4990,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5004,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5018,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5032,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5046,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5060,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5074,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5079,7 +5088,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5093,7 +5102,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5116,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5121,7 +5130,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5144,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5149,7 +5158,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5163,7 +5172,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5186,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5200,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,10 +5211,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5228,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5242,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5256,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5270,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5284,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5298,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5312,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5326,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5340,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5345,7 +5354,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5359,7 +5368,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5373,7 +5382,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5396,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5410,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5424,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5438,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5443,7 +5452,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5466,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5480,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5494,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5508,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5522,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5536,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
